--- a/g20_results_tables/rt_sp080_05_vc_affiliations_frequency.xlsx
+++ b/g20_results_tables/rt_sp080_05_vc_affiliations_frequency.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -490,23 +490,23 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -525,14 +525,6 @@
         <v>14</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>15</v>
-      </c>
-      <c r="B13" t="n">
         <v>1</v>
       </c>
     </row>
